--- a/data/trans_dic/IP04D$aparatos-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$aparatos-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,8 +522,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -612,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -675,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>54,33; 74,06</t>
+          <t>53,89; 74,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,28; 20,11</t>
+          <t>6,39; 20,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,56; 38,13</t>
+          <t>19,01; 38,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36,7; 58,47</t>
+          <t>37,85; 58,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,05; 23,63</t>
+          <t>9,08; 23,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,5; 41,58</t>
+          <t>22,98; 42,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,8; 62,48</t>
+          <t>47,75; 63,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,29; 19,89</t>
+          <t>9,02; 19,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,58; 37,46</t>
+          <t>23,75; 36,64</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -785,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62,16; 76,75</t>
+          <t>62,02; 77,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,2; 46,8</t>
+          <t>31,14; 47,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84,8; 95,94</t>
+          <t>85,1; 96,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58,19; 72,92</t>
+          <t>58,56; 72,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,15; 39,81</t>
+          <t>25,44; 40,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,35; 91,53</t>
+          <t>80,21; 91,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,69; 72,24</t>
+          <t>62,0; 72,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,55; 41,16</t>
+          <t>30,77; 41,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>84,09; 92,97</t>
+          <t>83,78; 92,67</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -895,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,69; 82,62</t>
+          <t>65,49; 83,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66,2; 84,06</t>
+          <t>66,9; 83,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55,61; 74,27</t>
+          <t>54,93; 74,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68,33; 84,53</t>
+          <t>69,33; 85,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>69,81; 85,97</t>
+          <t>70,74; 86,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,77; 72,14</t>
+          <t>52,33; 70,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,77; 81,97</t>
+          <t>69,61; 82,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>70,33; 82,99</t>
+          <t>69,89; 82,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56,74; 70,26</t>
+          <t>57,18; 70,36</t>
         </is>
       </c>
     </row>
@@ -1005,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,59; 66,3</t>
+          <t>46,85; 66,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,65; 71,0</t>
+          <t>53,07; 70,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,51; 47,98</t>
+          <t>27,28; 47,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,15; 69,52</t>
+          <t>51,76; 70,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,17; 69,78</t>
+          <t>50,42; 69,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,82; 45,66</t>
+          <t>19,88; 48,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,84; 65,37</t>
+          <t>51,77; 65,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>54,04; 67,28</t>
+          <t>53,56; 67,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,58; 44,65</t>
+          <t>25,88; 44,1</t>
         </is>
       </c>
     </row>
@@ -1115,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>47,81; 73,98</t>
+          <t>48,91; 74,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,83; 95,48</t>
+          <t>77,86; 95,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91,98; 100,0</t>
+          <t>91,77; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44,14; 68,79</t>
+          <t>42,79; 68,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>78,47; 95,0</t>
+          <t>80,12; 95,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>97,34; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,9; 67,18</t>
+          <t>51,21; 68,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>83,11; 94,09</t>
+          <t>82,09; 94,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>95,92; 100,0</t>
+          <t>95,61; 100,0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1225,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55,56; 76,91</t>
+          <t>55,8; 76,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,12; 26,53</t>
+          <t>10,81; 27,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,3; 55,71</t>
+          <t>32,39; 55,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65,44; 84,57</t>
+          <t>67,42; 84,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,31; 32,35</t>
+          <t>13,62; 32,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,97; 51,59</t>
+          <t>31,74; 51,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64,74; 78,44</t>
+          <t>63,91; 78,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,08; 27,13</t>
+          <t>13,81; 27,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34,85; 50,21</t>
+          <t>35,08; 50,31</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1335,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>69,44; 81,36</t>
+          <t>69,24; 81,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42,19; 56,25</t>
+          <t>42,27; 55,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,99; 38,89</t>
+          <t>23,34; 38,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67,99; 79,91</t>
+          <t>68,36; 80,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,9; 58,89</t>
+          <t>45,32; 59,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,98; 26,97</t>
+          <t>14,08; 27,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,46; 79,15</t>
+          <t>70,34; 78,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>46,1; 55,52</t>
+          <t>45,79; 55,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,71; 30,19</t>
+          <t>19,62; 30,24</t>
         </is>
       </c>
     </row>
@@ -1445,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>44,36; 56,74</t>
+          <t>43,98; 56,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>56,8; 68,72</t>
+          <t>57,11; 69,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>88,71; 96,17</t>
+          <t>89,03; 96,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37,22; 50,06</t>
+          <t>38,15; 50,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>60,25; 71,93</t>
+          <t>59,61; 71,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>90,21; 96,64</t>
+          <t>89,86; 96,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,78; 51,72</t>
+          <t>42,91; 51,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>60,52; 68,65</t>
+          <t>60,21; 68,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>91,08; 95,66</t>
+          <t>91,21; 95,81</t>
         </is>
       </c>
     </row>
@@ -1555,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>61,57; 67,45</t>
+          <t>61,42; 67,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48,7; 54,71</t>
+          <t>48,77; 54,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58,8; 68,11</t>
+          <t>58,66; 67,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>59,04; 64,78</t>
+          <t>58,79; 64,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>49,71; 55,52</t>
+          <t>49,67; 55,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54,48; 62,35</t>
+          <t>54,44; 62,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>60,96; 65,19</t>
+          <t>60,97; 65,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>50,15; 54,4</t>
+          <t>50,06; 54,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>57,37; 63,2</t>
+          <t>57,54; 63,67</t>
         </is>
       </c>
     </row>
@@ -1624,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>36450</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7050</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20800</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>30830</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10028</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>25396</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>67280</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>17078</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>46197</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>30426; 42205</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3666; 11645</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13933; 28043</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24531; 37604</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5854; 15403</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>18239; 33671</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>57902; 76478</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>10984; 23679</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>36258; 55932</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>72368</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40604</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>116326</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>72043</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>36515</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>110323</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>144411</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>77120</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>226650</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>64539; 80162</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>32364; 48865</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108637; 122638</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>64345; 80045</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>28056; 44837</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>102349; 116554</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>132640; 155145</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>65929; 89910</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>213856; 236548</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>50847</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>50467</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>38026</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>55624</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>55234</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>42029</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>106471</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>105701</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>80055</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>44649; 56857</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>44707; 55929</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>32008; 43226</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>49402; 61131</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>49453; 60138</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>35150; 47455</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>97055; 114398</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>95570; 113197</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>71721; 88252</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>44710</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>47052</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>25889</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>50073</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>49179</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>26081</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94783</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>96231</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>51970</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>36433; 51443</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>40401; 53496</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>18865; 33116</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>42562; 57620</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>40933; 56605</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>15531; 37511</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>82829; 105272</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>84255; 105508</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>38120; 64952</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>27096</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>36484</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>33960</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>26556</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>41470</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>40719</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>53652</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>77954</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>74679</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>21473; 32637</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>31810; 38888</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>31672; 34513</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>20007; 32045</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>37137; 44055</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>46419; 62017</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>71585; 82026</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>71930; 75232</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>36928</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9742</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>20234</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>46183</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>12694</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>23353</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>83111</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>22436</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>43587</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>30850; 42445</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>5869; 14675</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>14952; 25549</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>40620; 51183</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>7862; 18824</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>17831; 29036</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>73834; 90695</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>15472; 30381</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>35910; 51495</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>104768</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>67379</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>38016</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>108552</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>72935</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>30899</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>213319</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>140313</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>68916</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>96048; 113369</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>57742; 76409</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>29054; 48354</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>99629; 117521</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>63412; 83416</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>21835; 42094</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>200094; 224689</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>126605; 154036</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>54860; 84549</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>82781</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>103560</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>122654</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>75441</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>112447</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>146888</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>158223</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>216007</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>269541</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>72098; 92304</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>93764; 113419</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>117180; 126549</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>65362; 86246</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>101447; 121748</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>140253; 151031</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>143845; 171659</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>201310; 229043</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>262430; 275640</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>1097</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>1190</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>455948</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>362339</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>415906</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>465303</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>390501</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>445689</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>921251</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>752840</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>861595</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>435016; 476483</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>341465; 382945</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>390190; 449372</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>442269; 486898</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>367598; 413510</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>413919; 476641</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>890540; 951405</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>720906; 781491</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>820184; 907555</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04D$aparatos-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$aparatos-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,89; 74,75</t>
+          <t>53,95; 74,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,39; 20,3</t>
+          <t>6,51; 19,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,01; 38,27</t>
+          <t>19,25; 38,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,85; 58,02</t>
+          <t>37,09; 58,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,08; 23,9</t>
+          <t>9,44; 23,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,98; 42,43</t>
+          <t>22,61; 41,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,75; 63,07</t>
+          <t>47,4; 62,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,02; 19,44</t>
+          <t>9,49; 19,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,75; 36,64</t>
+          <t>23,82; 37,22</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62,02; 77,03</t>
+          <t>61,69; 76,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,14; 47,01</t>
+          <t>31,53; 47,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,1; 96,07</t>
+          <t>85,03; 96,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58,56; 72,85</t>
+          <t>58,17; 72,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,44; 40,66</t>
+          <t>26,15; 40,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,21; 91,35</t>
+          <t>79,69; 91,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,0; 72,52</t>
+          <t>61,97; 72,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,77; 41,97</t>
+          <t>30,59; 41,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>83,78; 92,67</t>
+          <t>84,53; 93,07</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65,49; 83,4</t>
+          <t>64,6; 82,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66,9; 83,69</t>
+          <t>65,96; 83,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54,93; 74,18</t>
+          <t>55,99; 74,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69,33; 85,79</t>
+          <t>68,82; 85,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>70,74; 86,03</t>
+          <t>70,14; 86,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,33; 70,66</t>
+          <t>52,26; 71,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,61; 82,05</t>
+          <t>69,87; 82,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69,89; 82,79</t>
+          <t>70,88; 82,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57,18; 70,36</t>
+          <t>56,41; 70,1</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,85; 66,16</t>
+          <t>47,76; 66,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,07; 70,27</t>
+          <t>52,72; 70,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,28; 47,89</t>
+          <t>28,96; 48,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,76; 70,07</t>
+          <t>51,78; 70,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,42; 69,72</t>
+          <t>51,47; 69,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,88; 48,01</t>
+          <t>19,71; 47,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,77; 65,8</t>
+          <t>52,45; 65,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>53,56; 67,07</t>
+          <t>54,64; 67,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,88; 44,1</t>
+          <t>25,67; 44,43</t>
         </is>
       </c>
     </row>
@@ -1118,27 +1118,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>48,91; 74,34</t>
+          <t>49,18; 73,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77,86; 95,19</t>
+          <t>78,34; 96,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91,77; 100,0</t>
+          <t>91,83; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42,79; 68,54</t>
+          <t>44,39; 68,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>80,12; 95,05</t>
+          <t>79,55; 95,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,21; 68,41</t>
+          <t>50,36; 67,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>82,09; 94,06</t>
+          <t>83,03; 94,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>95,61; 100,0</t>
+          <t>96,38; 100,0</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55,8; 76,77</t>
+          <t>55,37; 76,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,81; 27,04</t>
+          <t>10,83; 28,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32,39; 55,34</t>
+          <t>33,04; 55,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>67,42; 84,96</t>
+          <t>66,75; 84,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,62; 32,6</t>
+          <t>12,94; 32,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,74; 51,68</t>
+          <t>30,69; 51,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>63,91; 78,5</t>
+          <t>64,24; 78,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,81; 27,12</t>
+          <t>14,74; 27,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35,08; 50,31</t>
+          <t>35,6; 50,68</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>69,24; 81,73</t>
+          <t>68,92; 81,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42,27; 55,94</t>
+          <t>42,21; 55,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,34; 38,84</t>
+          <t>23,53; 38,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68,36; 80,64</t>
+          <t>67,97; 80,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>45,32; 59,62</t>
+          <t>44,92; 59,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,08; 27,15</t>
+          <t>14,37; 27,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,34; 78,99</t>
+          <t>70,72; 79,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45,79; 55,71</t>
+          <t>45,99; 56,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,62; 30,24</t>
+          <t>19,9; 30,37</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>43,98; 56,31</t>
+          <t>43,43; 57,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>57,11; 69,08</t>
+          <t>57,17; 68,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89,03; 96,15</t>
+          <t>88,76; 95,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38,15; 50,34</t>
+          <t>37,87; 49,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>59,61; 71,54</t>
+          <t>60,06; 72,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>89,86; 96,76</t>
+          <t>90,25; 96,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,91; 51,21</t>
+          <t>42,97; 51,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>60,21; 68,5</t>
+          <t>59,79; 68,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>91,21; 95,81</t>
+          <t>90,62; 95,69</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>61,42; 67,27</t>
+          <t>61,24; 67,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48,77; 54,69</t>
+          <t>48,64; 54,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58,66; 67,56</t>
+          <t>58,92; 68,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>58,79; 64,73</t>
+          <t>59,04; 64,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>49,67; 55,88</t>
+          <t>49,55; 55,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54,44; 62,69</t>
+          <t>54,1; 62,25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>60,97; 65,14</t>
+          <t>60,97; 65,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>50,06; 54,26</t>
+          <t>50,14; 54,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>57,54; 63,67</t>
+          <t>57,7; 63,37</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>30426; 42205</t>
+          <t>30457; 41857</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3666; 11645</t>
+          <t>3736; 11240</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13933; 28043</t>
+          <t>14109; 28489</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24531; 37604</t>
+          <t>24040; 38191</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5854; 15403</t>
+          <t>6084; 15250</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18239; 33671</t>
+          <t>17948; 33151</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57902; 76478</t>
+          <t>57481; 75847</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10984; 23679</t>
+          <t>11562; 24019</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36258; 55932</t>
+          <t>36362; 56822</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64539; 80162</t>
+          <t>64202; 79816</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32364; 48865</t>
+          <t>32776; 49703</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>108637; 122638</t>
+          <t>108547; 122862</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64345; 80045</t>
+          <t>63917; 79731</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28056; 44837</t>
+          <t>28844; 44357</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>102349; 116554</t>
+          <t>101680; 116852</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>132640; 155145</t>
+          <t>132580; 154892</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>65929; 89910</t>
+          <t>65530; 89299</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>213856; 236548</t>
+          <t>215770; 237562</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>44649; 56857</t>
+          <t>44044; 56164</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>44707; 55929</t>
+          <t>44079; 56008</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32008; 43226</t>
+          <t>32625; 43209</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49402; 61131</t>
+          <t>49040; 60889</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>49453; 60138</t>
+          <t>49029; 60263</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35150; 47455</t>
+          <t>35102; 48275</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97055; 114398</t>
+          <t>97415; 114561</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>95570; 113197</t>
+          <t>96918; 112996</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>71721; 88252</t>
+          <t>70752; 87931</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36433; 51443</t>
+          <t>37137; 51693</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40401; 53496</t>
+          <t>40131; 53720</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18865; 33116</t>
+          <t>20024; 33324</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42562; 57620</t>
+          <t>42577; 57811</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40933; 56605</t>
+          <t>41783; 56732</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15531; 37511</t>
+          <t>15402; 37209</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82829; 105272</t>
+          <t>83918; 104152</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>84255; 105508</t>
+          <t>85961; 106770</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38120; 64952</t>
+          <t>37803; 65436</t>
         </is>
       </c>
     </row>
@@ -2513,27 +2513,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>21473; 32637</t>
+          <t>21591; 32347</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31810; 38888</t>
+          <t>32005; 39421</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31672; 34513</t>
+          <t>31695; 34513</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20007; 32045</t>
+          <t>20754; 31831</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>37137; 44055</t>
+          <t>36872; 44065</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2543,17 +2543,17 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46419; 62017</t>
+          <t>45655; 61350</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>71585; 82026</t>
+          <t>72409; 82225</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>71930; 75232</t>
+          <t>72505; 75232</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>30850; 42445</t>
+          <t>30616; 42509</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5869; 14675</t>
+          <t>5878; 15312</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14952; 25549</t>
+          <t>15253; 25565</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40620; 51183</t>
+          <t>40215; 51134</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7862; 18824</t>
+          <t>7473; 18547</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17831; 29036</t>
+          <t>17244; 28874</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>73834; 90695</t>
+          <t>74224; 90730</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15472; 30381</t>
+          <t>16516; 30578</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>35910; 51495</t>
+          <t>36434; 51875</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>96048; 113369</t>
+          <t>95605; 112574</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>57742; 76409</t>
+          <t>57665; 76204</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29054; 48354</t>
+          <t>29302; 47905</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>99629; 117521</t>
+          <t>99058; 116588</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>63412; 83416</t>
+          <t>62850; 82781</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21835; 42094</t>
+          <t>22283; 42984</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>200094; 224689</t>
+          <t>201156; 226102</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>126605; 154036</t>
+          <t>127182; 157095</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>54860; 84549</t>
+          <t>55630; 84916</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>72098; 92304</t>
+          <t>71184; 93519</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>93764; 113419</t>
+          <t>93858; 113030</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>117180; 126549</t>
+          <t>116829; 126319</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>65362; 86246</t>
+          <t>64877; 85161</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>101447; 121748</t>
+          <t>102201; 122776</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>140253; 151031</t>
+          <t>140874; 151038</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>143845; 171659</t>
+          <t>144040; 173422</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>201310; 229043</t>
+          <t>199902; 229583</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>262430; 275640</t>
+          <t>260726; 275294</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>435016; 476483</t>
+          <t>433746; 477138</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>341465; 382945</t>
+          <t>340584; 383439</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>390190; 449372</t>
+          <t>391941; 454634</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>442269; 486898</t>
+          <t>444078; 487362</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>367598; 413510</t>
+          <t>366690; 411755</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>413919; 476641</t>
+          <t>411370; 473302</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>890540; 951405</t>
+          <t>890450; 953410</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>720906; 781491</t>
+          <t>722137; 784270</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>820184; 907555</t>
+          <t>822563; 903394</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04D$aparatos-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$aparatos-Provincia-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que no dispone de instalación de calefacción en su vivienda pero sí tiene aparatos de calefacción (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>47,57%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15,56%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>33,51%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>64,56%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>12,29%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>28,38%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>47,57%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,56%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,95; 74,14</t>
+          <t>36,7; 58,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,51; 19,59</t>
+          <t>9,05; 23,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,25; 38,88</t>
+          <t>24,69; 42,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,09; 58,93</t>
+          <t>54,33; 74,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,44; 23,66</t>
+          <t>6,28; 20,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,61; 41,77</t>
+          <t>24,52; 44,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,4; 62,55</t>
+          <t>47,8; 62,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,49; 19,71</t>
+          <t>9,29; 19,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,82; 37,22</t>
+          <t>27,06; 40,48</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>65,57%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>33,11%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86,44%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>69,54%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>39,06%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>91,13%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>65,57%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>33,11%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>87,73%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,69; 76,7</t>
+          <t>58,19; 72,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,53; 47,82</t>
+          <t>26,15; 39,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,03; 96,25</t>
+          <t>78,95; 91,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58,17; 72,56</t>
+          <t>62,16; 76,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,15; 40,22</t>
+          <t>31,2; 46,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,69; 91,58</t>
+          <t>82,72; 93,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,97; 72,4</t>
+          <t>61,69; 72,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,59; 41,68</t>
+          <t>30,55; 41,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>84,53; 93,07</t>
+          <t>83,08; 91,47</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>78,06%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>79,01%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>62,1%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>74,58%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>75,51%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>65,26%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>78,06%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>79,01%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,68%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,6; 82,38</t>
+          <t>68,33; 84,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65,96; 83,8</t>
+          <t>69,81; 85,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55,99; 74,16</t>
+          <t>52,22; 71,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68,82; 85,45</t>
+          <t>64,69; 82,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>70,14; 86,21</t>
+          <t>66,2; 84,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,26; 71,88</t>
+          <t>55,61; 74,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,87; 82,16</t>
+          <t>69,77; 81,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>70,88; 82,64</t>
+          <t>70,33; 82,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56,41; 70,1</t>
+          <t>56,49; 69,98</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>60,89%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>60,58%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33,54%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>57,5%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>61,81%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>37,44%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>60,89%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>60,58%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>47,76; 66,48</t>
+          <t>51,15; 69,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,72; 70,57</t>
+          <t>51,17; 69,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,96; 48,19</t>
+          <t>19,83; 46,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,78; 70,3</t>
+          <t>48,59; 66,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,47; 69,88</t>
+          <t>51,65; 71,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,71; 47,62</t>
+          <t>25,98; 46,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,45; 65,1</t>
+          <t>51,84; 65,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>54,64; 67,87</t>
+          <t>54,04; 67,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,67; 44,43</t>
+          <t>26,02; 44,21</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56,8%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>89,47%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>61,72%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>89,3%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>56,8%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>89,47%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>49,18; 73,68</t>
+          <t>44,14; 68,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,34; 96,49</t>
+          <t>78,47; 95,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91,83; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44,39; 68,08</t>
+          <t>47,81; 73,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>79,55; 95,07</t>
+          <t>78,83; 95,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>92,19; 100,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,36; 67,68</t>
+          <t>49,9; 67,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>83,03; 94,29</t>
+          <t>83,11; 94,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>96,38; 100,0</t>
+          <t>95,96; 100,0</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>76,66%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21,99%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>42,34%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>66,79%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>17,95%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>43,83%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>76,66%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>21,99%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55,37; 76,88</t>
+          <t>65,44; 84,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,83; 28,21</t>
+          <t>13,31; 32,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,04; 55,37</t>
+          <t>31,93; 52,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66,75; 84,88</t>
+          <t>55,56; 76,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,94; 32,12</t>
+          <t>10,12; 26,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,69; 51,39</t>
+          <t>33,07; 55,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64,24; 78,53</t>
+          <t>64,74; 78,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,74; 27,3</t>
+          <t>14,08; 27,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35,6; 50,68</t>
+          <t>35,25; 50,56</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>74,48%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>52,13%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19,32%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>75,53%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>49,32%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>30,53%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>74,48%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>52,13%</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>68,92; 81,15</t>
+          <t>67,99; 79,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42,21; 55,79</t>
+          <t>44,9; 58,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,53; 38,48</t>
+          <t>13,67; 25,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67,97; 80,0</t>
+          <t>69,44; 81,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,92; 59,17</t>
+          <t>42,19; 56,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,37; 27,72</t>
+          <t>22,15; 35,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,72; 79,49</t>
+          <t>70,46; 79,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45,99; 56,81</t>
+          <t>46,1; 55,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,9; 30,37</t>
+          <t>19,13; 28,25</t>
         </is>
       </c>
     </row>
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>44,04%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>66,08%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>94,46%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>50,5%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>63,08%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>93,19%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>44,04%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>66,08%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>43,43; 57,05</t>
+          <t>37,22; 50,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>57,17; 68,85</t>
+          <t>60,25; 71,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>88,76; 95,97</t>
+          <t>90,35; 96,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37,87; 49,71</t>
+          <t>44,36; 56,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>60,06; 72,15</t>
+          <t>56,8; 68,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>90,25; 96,76</t>
+          <t>88,9; 96,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,97; 51,73</t>
+          <t>42,78; 51,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>59,79; 68,66</t>
+          <t>60,52; 68,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>90,62; 95,69</t>
+          <t>91,43; 96,0</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>61,86%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>52,77%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>60,08%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>64,37%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>51,75%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>62,53%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>61,86%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>52,77%</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>61,18%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>61,24; 67,36</t>
+          <t>59,04; 64,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48,64; 54,76</t>
+          <t>49,71; 55,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58,92; 68,35</t>
+          <t>56,28; 63,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>59,04; 64,79</t>
+          <t>61,57; 67,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>49,55; 55,64</t>
+          <t>48,7; 54,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54,1; 62,25</t>
+          <t>59,24; 65,45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>60,97; 65,28</t>
+          <t>60,96; 65,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>50,14; 54,46</t>
+          <t>50,15; 54,4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>57,7; 63,37</t>
+          <t>58,67; 63,5</t>
         </is>
       </c>
     </row>
@@ -1654,20 +1654,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que no dispone de instalación de calefacción en su vivienda pero sí tiene aparatos de calefacción (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,32 +1755,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>30830</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10028</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>21495</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>36450</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>7050</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20800</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30830</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10028</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25396</t>
+          <t>19077</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46197</t>
+          <t>40573</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>30457; 41857</t>
+          <t>23788; 37895</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3736; 11240</t>
+          <t>5834; 15235</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14109; 28489</t>
+          <t>15837; 27506</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24040; 38191</t>
+          <t>30675; 41815</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6084; 15250</t>
+          <t>3604; 11537</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17948; 33151</t>
+          <t>13850; 24878</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57481; 75847</t>
+          <t>57965; 75767</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11562; 24019</t>
+          <t>11314; 24231</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36362; 56822</t>
+          <t>32645; 48831</t>
         </is>
       </c>
     </row>
@@ -1918,32 +1918,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>127</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>72043</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>36515</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>100132</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>72368</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>40604</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>116326</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>72043</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>36515</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>110323</t>
+          <t>90444</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>226650</t>
+          <t>190577</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64202; 79816</t>
+          <t>63932; 80119</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32776; 49703</t>
+          <t>28837; 43908</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>108547; 122862</t>
+          <t>91457; 106183</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>63917; 79731</t>
+          <t>64687; 79877</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28844; 44357</t>
+          <t>32430; 48648</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>101680; 116852</t>
+          <t>83878; 94907</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>132580; 154892</t>
+          <t>131987; 154554</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>65530; 89299</t>
+          <t>65457; 88180</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>215770; 237562</t>
+          <t>180465; 198707</t>
         </is>
       </c>
     </row>
@@ -2081,32 +2081,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>63</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2134,32 +2134,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>55624</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>55234</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>36876</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>50847</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>50467</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>38026</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>55624</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>55234</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42029</t>
+          <t>36948</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>80055</t>
+          <t>73825</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>44044; 56164</t>
+          <t>48686; 60231</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>44079; 56008</t>
+          <t>48802; 60096</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32625; 43209</t>
+          <t>31006; 42572</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49040; 60889</t>
+          <t>44103; 56329</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>49029; 60263</t>
+          <t>44244; 56177</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35102; 48275</t>
+          <t>31453; 42035</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97415; 114561</t>
+          <t>97281; 114294</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>96918; 112996</t>
+          <t>96170; 113483</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>70752; 87931</t>
+          <t>65487; 81129</t>
         </is>
       </c>
     </row>
@@ -2244,32 +2244,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>50073</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>49179</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>24205</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>44710</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>47052</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>25889</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>50073</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>49179</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26081</t>
+          <t>24819</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>51970</t>
+          <t>49024</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37137; 51693</t>
+          <t>42066; 57168</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40131; 53720</t>
+          <t>41542; 56647</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20024; 33324</t>
+          <t>14307; 33402</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42577; 57811</t>
+          <t>37786; 51553</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41783; 56732</t>
+          <t>39319; 54049</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15402; 37209</t>
+          <t>18128; 32136</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>83918; 104152</t>
+          <t>82945; 104582</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>85961; 106770</t>
+          <t>85018; 105843</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37803; 65436</t>
+          <t>36924; 62744</t>
         </is>
       </c>
     </row>
@@ -2407,32 +2407,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>67</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2460,32 +2460,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>26556</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>41470</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>27096</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>36484</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>33960</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>26556</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>41470</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35056</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>74679</t>
+          <t>74635</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>21591; 32347</t>
+          <t>20638; 32160</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>32005; 39421</t>
+          <t>36370; 44034</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31695; 34513</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20754; 31831</t>
+          <t>20991; 32479</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>36872; 44065</t>
+          <t>32207; 39007</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32829; 35608</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45655; 61350</t>
+          <t>45233; 60903</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>72409; 82225</t>
+          <t>72478; 82049</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>72505; 75232</t>
+          <t>72152; 75187</t>
         </is>
       </c>
     </row>
@@ -2570,32 +2570,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>46183</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>12694</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>20720</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>36928</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>9742</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>20234</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>12694</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23353</t>
+          <t>19997</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>43587</t>
+          <t>40717</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>30616; 42509</t>
+          <t>39422; 50948</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5878; 15312</t>
+          <t>7685; 18676</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15253; 25565</t>
+          <t>15629; 25891</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40215; 51134</t>
+          <t>30719; 42524</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7473; 18547</t>
+          <t>5490; 14397</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17244; 28874</t>
+          <t>15134; 25547</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>74224; 90730</t>
+          <t>74802; 90626</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16516; 30578</t>
+          <t>15777; 30386</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>36434; 51875</t>
+          <t>33388; 47883</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>52</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>108552</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>72935</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>27134</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>104768</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>67379</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>38016</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>108552</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>72935</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30899</t>
+          <t>34431</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>68916</t>
+          <t>61566</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>95605; 112574</t>
+          <t>99087; 116453</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>57665; 76204</t>
+          <t>62821; 82394</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29302; 47905</t>
+          <t>19193; 36030</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>99058; 116588</t>
+          <t>96332; 112860</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>62850; 82781</t>
+          <t>57635; 76832</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22283; 42984</t>
+          <t>27137; 43516</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>201156; 226102</t>
+          <t>200433; 225156</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>127182; 157095</t>
+          <t>127460; 153514</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>55630; 84916</t>
+          <t>50309; 74276</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>176</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>75441</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>112447</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>150003</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>82781</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>103560</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>122654</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>75441</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>112447</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>146888</t>
+          <t>131446</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>269541</t>
+          <t>281451</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>71184; 93519</t>
+          <t>63766; 85768</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>93858; 113030</t>
+          <t>102540; 122414</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>116829; 126319</t>
+          <t>143487; 153764</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>64877; 85161</t>
+          <t>72713; 93001</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>102201; 122776</t>
+          <t>93249; 112827</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>140874; 151038</t>
+          <t>124905; 135409</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>144040; 173422</t>
+          <t>143428; 173379</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>199902; 229583</t>
+          <t>202353; 229540</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>260726; 275294</t>
+          <t>273662; 287335</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>660</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>538</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>589</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>559</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>465303</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>390501</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>420145</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>455948</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>362339</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>415906</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>465303</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>390501</t>
-        </is>
-      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>445689</t>
+          <t>392221</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>861595</t>
+          <t>812366</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>433746; 477138</t>
+          <t>444098; 487265</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>340584; 383439</t>
+          <t>367827; 410849</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>391941; 454634</t>
+          <t>393508; 445390</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>444078; 487362</t>
+          <t>436076; 477724</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>366690; 411755</t>
+          <t>340992; 383063</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>411370; 473302</t>
+          <t>372390; 411409</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>890450; 953410</t>
+          <t>890344; 952094</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>722137; 784270</t>
+          <t>722197; 783510</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>822563; 903394</t>
+          <t>779070; 843161</t>
         </is>
       </c>
     </row>
